--- a/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-18-08.xlsx
+++ b/data/source-participacon-momoento4-planeacion-teritorial/participacion2026-18-08.xlsx
@@ -499,7 +499,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H2">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I2" t="str">
         <v>08:00 - 22:00</v>
@@ -564,7 +564,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H3">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I3" t="str">
         <v>08:00 - 22:00</v>
@@ -629,7 +629,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H4">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I4" t="str">
         <v>08:00 - 22:00</v>
@@ -694,7 +694,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H5">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I5" t="str">
         <v>08:00 - 22:00</v>
@@ -750,7 +750,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H6">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I6" t="str">
         <v>08:00 - 22:00</v>
@@ -806,7 +806,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H7">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I7" t="str">
         <v>08:00 - 22:00</v>
@@ -871,7 +871,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H8">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I8" t="str">
         <v>08:00 - 22:00</v>
@@ -936,7 +936,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H9">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I9" t="str">
         <v>08:00 - 22:00</v>
@@ -992,7 +992,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H10">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I10" t="str">
         <v>08:00 - 22:00</v>
@@ -1042,7 +1042,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H11">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I11" t="str">
         <v>08:00 - 22:00</v>
@@ -1107,7 +1107,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H12">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I12" t="str">
         <v>08:00 - 22:00</v>
@@ -1172,7 +1172,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H13">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I13" t="str">
         <v>08:00 - 22:00</v>
@@ -1237,7 +1237,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H14">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I14" t="str">
         <v>08:00 - 22:00</v>
@@ -1293,7 +1293,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H15">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I15" t="str">
         <v>08:00 - 22:00</v>
@@ -1349,7 +1349,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H16">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I16" t="str">
         <v>08:00 - 22:00</v>
@@ -1405,7 +1405,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H17">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I17" t="str">
         <v>08:00 - 22:00</v>
@@ -1470,7 +1470,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H18">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I18" t="str">
         <v>08:00 - 22:00</v>
@@ -1535,7 +1535,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H19">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I19" t="str">
         <v>08:00 - 22:00</v>
@@ -1591,7 +1591,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H20">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I20" t="str">
         <v>08:00 - 22:00</v>
@@ -1656,7 +1656,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H21">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I21" t="str">
         <v>08:00 - 22:00</v>
@@ -1721,7 +1721,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H22">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I22" t="str">
         <v>08:00 - 22:00</v>
@@ -1786,7 +1786,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H23">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I23" t="str">
         <v>08:00 - 22:00</v>
@@ -1851,7 +1851,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H24">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I24" t="str">
         <v>08:00 - 22:00</v>
@@ -1916,7 +1916,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H25">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I25" t="str">
         <v>08:00 - 22:00</v>
@@ -1981,7 +1981,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H26">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I26" t="str">
         <v>08:00 - 22:00</v>
@@ -2046,7 +2046,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H27">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I27" t="str">
         <v>08:00 - 22:00</v>
@@ -2102,7 +2102,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H28">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I28" t="str">
         <v>08:00 - 22:00</v>
@@ -2167,7 +2167,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H29">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I29" t="str">
         <v>08:00 - 22:00</v>
@@ -2232,7 +2232,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H30">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I30" t="str">
         <v>08:00 - 22:00</v>
@@ -2288,7 +2288,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H31">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I31" t="str">
         <v>08:00 - 22:00</v>
@@ -2353,7 +2353,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H32">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I32" t="str">
         <v>08:00 - 22:00</v>
@@ -2409,7 +2409,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H33">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I33" t="str">
         <v>08:00 - 22:00</v>
@@ -2474,7 +2474,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H34">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I34" t="str">
         <v>08:00 - 22:00</v>
@@ -2539,7 +2539,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H35">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I35" t="str">
         <v>08:00 - 22:00</v>
@@ -2595,7 +2595,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H36">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I36" t="str">
         <v>08:00 - 22:00</v>
@@ -2660,7 +2660,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H37">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I37" t="str">
         <v>08:00 - 22:00</v>
@@ -2725,7 +2725,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H38">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I38" t="str">
         <v>08:00 - 22:00</v>
@@ -2790,7 +2790,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H39">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I39" t="str">
         <v>08:00 - 22:00</v>
@@ -2855,7 +2855,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H40">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I40" t="str">
         <v>08:00 - 22:00</v>
@@ -2920,7 +2920,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H41">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I41" t="str">
         <v>08:00 - 22:00</v>
@@ -2985,7 +2985,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H42">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I42" t="str">
         <v>08:00 - 22:00</v>
@@ -3050,7 +3050,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H43">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I43" t="str">
         <v>08:00 - 22:00</v>
@@ -3115,7 +3115,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H44">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I44" t="str">
         <v>08:00 - 22:00</v>
@@ -3180,7 +3180,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H45">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I45" t="str">
         <v>08:00 - 22:00</v>
@@ -3245,7 +3245,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H46">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I46" t="str">
         <v>08:00 - 22:00</v>
@@ -3310,7 +3310,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H47">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I47" t="str">
         <v>08:00 - 22:00</v>
@@ -3375,7 +3375,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H48">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I48" t="str">
         <v>08:00 - 22:00</v>
@@ -3431,7 +3431,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H49">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I49" t="str">
         <v>08:00 - 22:00</v>
@@ -3487,7 +3487,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H50">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I50" t="str">
         <v>08:00 - 22:00</v>
@@ -3552,7 +3552,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H51">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I51" t="str">
         <v>08:00 - 22:00</v>
@@ -3617,7 +3617,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H52">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I52" t="str">
         <v>08:00 - 22:00</v>
@@ -3682,7 +3682,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H53">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I53" t="str">
         <v>08:00 - 22:00</v>
@@ -3747,7 +3747,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H54">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I54" t="str">
         <v>08:00 - 22:00</v>
@@ -3812,7 +3812,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H55">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I55" t="str">
         <v>08:00 - 22:00</v>
@@ -3877,7 +3877,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H56">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I56" t="str">
         <v>08:00 - 22:00</v>
@@ -3942,7 +3942,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H57">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I57" t="str">
         <v>08:00 - 22:00</v>
@@ -4007,7 +4007,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H58">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I58" t="str">
         <v>08:00 - 22:00</v>
@@ -4072,7 +4072,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H59">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I59" t="str">
         <v>08:00 - 22:00</v>
@@ -4137,7 +4137,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H60">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I60" t="str">
         <v>08:00 - 22:00</v>
@@ -4202,7 +4202,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H61">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I61" t="str">
         <v>08:00 - 22:00</v>
@@ -4267,7 +4267,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H62">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I62" t="str">
         <v>08:00 - 22:00</v>
@@ -4332,7 +4332,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H63">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I63" t="str">
         <v>08:00 - 22:00</v>
@@ -4397,7 +4397,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H64">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I64" t="str">
         <v>08:00 - 22:00</v>
@@ -4462,7 +4462,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H65">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I65" t="str">
         <v>08:00 - 22:00</v>
@@ -4527,7 +4527,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H66">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I66" t="str">
         <v>08:00 - 22:00</v>
@@ -4592,7 +4592,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H67">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I67" t="str">
         <v>08:00 - 22:00</v>
@@ -4657,7 +4657,7 @@
         <v>SOCIALIZACIÓN</v>
       </c>
       <c r="H68">
-        <v>46253</v>
+        <v>46252</v>
       </c>
       <c r="I68" t="str">
         <v>08:00 - 22:00</v>
